--- a/artfynd/A 55197-2023 artfynd.xlsx
+++ b/artfynd/A 55197-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55197-2023 artfynd.xlsx
+++ b/artfynd/A 55197-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1306,6 +1306,140 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125524020</v>
+      </c>
+      <c r="B7" t="n">
+        <v>9153</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103814</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläckstumpbagge</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Margarinotus purpurascens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Herbst, 1792)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lindåsbacken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>525360</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6561763</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Mellösa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Carlberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Carlberg, Joakim Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55197-2023 artfynd.xlsx
+++ b/artfynd/A 55197-2023 artfynd.xlsx
@@ -1435,7 +1435,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Joakim Johansson</t>
+          <t>Joakim Johansson, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 55197-2023 artfynd.xlsx
+++ b/artfynd/A 55197-2023 artfynd.xlsx
@@ -1435,7 +1435,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joakim Johansson, Anders Carlberg</t>
+          <t>Anders Carlberg, Joakim Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 55197-2023 artfynd.xlsx
+++ b/artfynd/A 55197-2023 artfynd.xlsx
@@ -1313,11 +1313,6 @@
       <c r="B7" t="n">
         <v>9153</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>NT</t>

--- a/artfynd/A 55197-2023 artfynd.xlsx
+++ b/artfynd/A 55197-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109747689</v>
+        <v>109765226</v>
       </c>
       <c r="B2" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>7526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100581</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Dånvivel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Datonychus angulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boheman, 1845)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,20 +708,33 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>slaghåvning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lindåsbacken, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525359.6693106754</v>
+        <v>525360</v>
       </c>
       <c r="R2" t="n">
-        <v>6561762.095982077</v>
+        <v>6561763</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -758,7 +766,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +776,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +785,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,44 +797,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Carlberg, joakim johansson</t>
+          <t>Anders Carlberg, Joakim Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109765226</v>
+        <v>109744529</v>
       </c>
       <c r="B3" t="n">
-        <v>7437</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100581</v>
+        <v>102147</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dånvivel</t>
+          <t>Spindelbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Datonychus angulosus</t>
+          <t>Aegomorphus clavipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Boheman, 1845)</t>
+          <t>(Schrank, 1781)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,21 +849,17 @@
           <t>frispringande/krypande</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>slaghåvning</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lindåsbacken, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525359.6693106754</v>
+        <v>525360</v>
       </c>
       <c r="R3" t="n">
-        <v>6561762.095982077</v>
+        <v>6561763</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -901,7 +901,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,58 +927,49 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Carlberg, joakim johansson</t>
+          <t>Joakim Johansson, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109745417</v>
+        <v>109745397</v>
       </c>
       <c r="B4" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>102995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -981,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525359.6693106754</v>
+        <v>525360</v>
       </c>
       <c r="R4" t="n">
-        <v>6561762.095982077</v>
+        <v>6561763</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1046,22 +1042,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Carlberg, joakim johansson</t>
+          <t>Anders Carlberg, Joakim Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109745397</v>
+        <v>109747689</v>
       </c>
       <c r="B5" t="n">
-        <v>56887</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,16 +1060,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102995</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1088,7 +1079,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1101,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525359.6693106754</v>
+        <v>525360</v>
       </c>
       <c r="R5" t="n">
-        <v>6561762.095982077</v>
+        <v>6561763</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1136,7 +1127,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1146,7 +1137,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,44 +1157,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Carlberg, joakim johansson</t>
+          <t>Anders Carlberg, Joakim Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109744529</v>
+        <v>109745417</v>
       </c>
       <c r="B6" t="n">
-        <v>5219</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102147</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelbock</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Aegomorphus clavipes</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schrank, 1781)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1211,16 +1197,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1230,10 +1211,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525359.6693106754</v>
+        <v>525360</v>
       </c>
       <c r="R6" t="n">
-        <v>6561762.095982077</v>
+        <v>6561763</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1265,7 +1246,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1275,12 +1256,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På asp.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1265,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1301,139 +1276,10 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Carlberg, joakim johansson</t>
+          <t>Anders Carlberg, Joakim Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>125524020</v>
-      </c>
-      <c r="B7" t="n">
-        <v>9153</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>103814</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Fläckstumpbagge</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Margarinotus purpurascens</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Herbst, 1792)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>slag-/vattenhåvning</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Lindåsbacken, Nrk</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>525360</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6561763</v>
-      </c>
-      <c r="S7" t="n">
-        <v>50</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Närke</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Stora Mellösa</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Anders Carlberg</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Anders Carlberg, Joakim Johansson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
